--- a/Results/rbf_fd_parameter_study_3.xlsx
+++ b/Results/rbf_fd_parameter_study_3.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -813,4 +814,642 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>max_error_rel</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>l2_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.03972016109805564</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0356951714572528</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.3482580847367133</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.01248785528197931</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.01259962720734099</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.01278761592952292</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.007203185583504986</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.006247038535453802</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.01427574944092687</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.00897461909311149</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.008538667813216558</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.008518060330029701</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.009545311840375346</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.003760934720435224</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.003410561982117362</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>75</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.006155625019913858</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.003204159048458344</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.00212199848234548</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>85</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.005504208854625428</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.004145443572874957</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.003957785445074437</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.006857897834273171</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.001700722803206851</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.001089102096694987</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>115</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.007068917381043124</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.002622615855062792</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.002214675872842346</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>130</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.02083923030173068</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.001523870984943403</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.001299018508119381</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>150</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.05217901123517758</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.002747726470431223</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.003597220383689933</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>200</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.06806413906510721</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.004206207939854428</v>
+      </c>
+      <c r="L13" t="n">
+        <v>22.19477764949347</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_3.xlsx
+++ b/Results/rbf_fd_parameter_study_3.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1452,4 +1453,458 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>max_error_rel</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>l2_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9219976378919733</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1030803700214712</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4213740.753483731</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4130682894583468</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.01999113908316128</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.844114375228947</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.454560969556232</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.07636710746305934</v>
+      </c>
+      <c r="L4" t="n">
+        <v>24.65221118653226</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.02069592205117355</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.002056898758329049</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.001464268074814256</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.006850603530383963</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.001751267653425881</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.001154567565983485</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.006857897834273171</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.001700722803206851</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.001089102096694987</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.006927533974557436</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.001712601230058136</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.00110162546342363</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.007023134624474879</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.00173988298949217</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.001123644477685107</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_3.xlsx
+++ b/Results/rbf_fd_parameter_study_3.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1907,4 +1908,688 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>max_error_rel</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>l2_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.03530240544409042</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.008430435892065864</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.004428097626125897</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.02388478495317361</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.005595990718295467</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.002666410290883109</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.006775988754139111</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.001806887740491542</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0002766547126044306</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.006625282720032301</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.001535808786429786</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0005801767909139958</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.006811292554683397</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.001630078401278397</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0009818792822789033</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.00683569970457562</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.001665040743659504</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.00103692824398742</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.006855420427740013</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.001696564535739727</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.001082782043546813</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.006857897834273171</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.001700722803206851</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.001089102096694987</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.006859881741152399</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.001704083881540619</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.001102194407795703</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>100</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.00686012985342414</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.001704506165583283</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.01343164511202694</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>100</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.006860328363236661</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.001704844336301961</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.04067128962319833</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.006860353177982391</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.001704886629110454</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.002359697730018796</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.006860373030337854</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.001704920466787242</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.00167784311663599</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_3.xlsx
+++ b/Results/rbf_fd_parameter_study_3.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvector Angle" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2592,4 +2593,504 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>max_error_rel</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>l2_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.06436874721349997</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.01576548391920954</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.009005519631252455</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.01676213904251056</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.003060637722921084</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.002399112351875366</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.006916917914088205</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.001708552932084926</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0006081835718654502</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.006854354893374031</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.001517919312885407</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0007513319462603637</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.006857897834273171</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.001700722803206851</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.001089102096694987</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.006756841820868061</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.001514304129901755</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0007519324251807405</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.006868170373634862</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.001704524267531192</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0006184557790478138</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01671605333729195</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.003058594696922977</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.002412256972266181</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G10" t="n">
+        <v>24</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.06436874721327261</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0157654839190884</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.009005519631035873</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_3.xlsx
+++ b/Results/rbf_fd_parameter_study_3.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,6 +1053,721 @@
         <v>250</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>34120.31806814573</v>
+      </c>
+      <c r="L12" t="n">
+        <v>14519.51590014258</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2636.570406940375</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.2215969970388456</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.05922278244909182</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>369870.1195844985</v>
+      </c>
+      <c r="L13" t="n">
+        <v>152824.4969710023</v>
+      </c>
+      <c r="M13" t="n">
+        <v>27512.66604343868</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.2215146213034898</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.05919774032345285</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.4113692531465107</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.1587591057622844</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0827577205303426</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.0190555674709825</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0180609186513663</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.02214581037610891</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.008393947498846409</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.004045047498045493</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.0009084096916005365</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.0002967628115234128</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.003062512556063512</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.001230662868096074</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.0006214114938439011</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.0002149566822926259</v>
+      </c>
+      <c r="O16" t="n">
+        <v>6.56942353728161e-05</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>100</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0007244591926782508</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.0003164406588890422</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.0003503540840254791</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.536788795449264e-05</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.02316452044038e-05</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>100</v>
+      </c>
+      <c r="B18" t="n">
+        <v>100</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>100</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5.663462929443563e-05</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3.050353007123767e-05</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.257753972229574e-05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.069875156734194e-05</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.067285804113315e-05</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>100</v>
+      </c>
+      <c r="B19" t="n">
+        <v>100</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.0004040052283791771</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0001957946820511311</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.0001615578088332051</v>
+      </c>
+      <c r="N19" t="n">
+        <v>8.392273796272311e-06</v>
+      </c>
+      <c r="O19" t="n">
+        <v>8.554303193980506e-06</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>100</v>
+      </c>
+      <c r="B20" t="n">
+        <v>100</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H20" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.29426670428861e-05</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.53941967627898e-05</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.541618530642906e-05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>6.346922885006921e-06</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.70170465603267e-06</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>100</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>100</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H21" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.0002556907938676964</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.0001116232524519538</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.0002461211252949424</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.274182753355862e-05</v>
+      </c>
+      <c r="O21" t="n">
+        <v>6.584326652841952e-06</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>100</v>
+      </c>
+      <c r="B22" t="n">
+        <v>100</v>
+      </c>
+      <c r="C22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H22" t="n">
+        <v>12</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0001662336203656474</v>
+      </c>
+      <c r="L22" t="n">
+        <v>9.440908977124041e-05</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.0003325321686520673</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.368897900467106e-05</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.349959329270537e-05</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>100</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H23" t="n">
+        <v>12</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.0001767958087888601</v>
+      </c>
+      <c r="L23" t="n">
+        <v>7.996938648532395e-05</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.0005022655573499924</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5.381241915566689e-05</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.212691284334597e-05</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>100</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100</v>
+      </c>
+      <c r="C24" t="n">
+        <v>15</v>
+      </c>
+      <c r="D24" t="n">
+        <v>100</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H24" t="n">
+        <v>12</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.0004650957922828514</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0001312739747040069</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.0225679784908187</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.01704621759499904</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.001073046959303427</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Results/rbf_fd_parameter_study_3.xlsx
+++ b/Results/rbf_fd_parameter_study_3.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1771,4 +1772,765 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.000762789991507654</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0001841722759614253</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0001558653211745506</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.137180700860739e-05</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.292262705339924e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9.900329247928018e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.869296489803385e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>9.721677087944655e-05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.111929721861641e-05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.049010687990444e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.002303219056720944</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.001025583511491566</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.000664656417118592</v>
+      </c>
+      <c r="N4" t="n">
+        <v>9.684914977578e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.757409816604154e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0007687855449427724</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0002677815036504377</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0005843949616267008</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0001366049192491036</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.85849580206485e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7.261730963103336e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.649600055812196e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.6265778818675e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.033135112261055e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>8.316560353916378e-06</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0003530430174403194</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0001685021435539098</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0001215915282920609</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.59534036904405e-05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.195440710063662e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.01048474698341724</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.003128039589783525</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.002561955639443846</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.980615994016985e-05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.893017637855351e-05</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.663462929443563e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.050353007123767e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.257753972229574e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.069875156734194e-05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.067285804113315e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>115</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9.104605986184829e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4.789008951434791e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4.542245979772715e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.637401118013711e-05</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.481483652875026e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>130</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0008764498814392673</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0004269233583011691</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0003177563970236403</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.349713541797166e-05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4.313583108659665e-05</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.001107283417529986</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0003929645808567784</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0002222760483635986</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.314301138268753e-05</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.564872060869404e-05</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0001220165536909693</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5.546486123740826e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.01065083198709e-05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.088783537588142e-05</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.499809097482192e-06</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_3.xlsx
+++ b/Results/rbf_fd_parameter_study_3.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2533,4 +2534,545 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6.893649652090911e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3.611801510300684e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4.278208742754243e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.069514321321375e-05</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.061089451804295e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0001111964225028705</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5.581173320948089e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6.264503381150188e-05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.069739708592668e-05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.067028631301411e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0002471274184973237</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0001115853121174784</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.000123387800116267</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.069918237304682e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.063212934017472e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0001075431164887549</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.188025111018537e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5.868825180587443e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.06992623496756e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.073238082548807e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0001916780539993187</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7.858231678767613e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>8.793381360131585e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.085071368946814e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.067297103773072e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.663462929443563e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.050353007123767e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.257753972229574e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.069875156734194e-05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.067285804113315e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0001157595614244251</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5.606720594208994e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>6.761430207560172e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.069852931371989e-05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.067688151998079e-05</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001561697258013959</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7.239067954823686e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>7.759398104153023e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.444903271482053e-05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.005613281580486e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_3.xlsx
+++ b/Results/rbf_fd_parameter_study_3.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3075,4 +3076,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.868569597330016e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.829739119261107e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>8.22196868971752e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>8.59744411618817e-05</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.717624755993191e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.524582014157053e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.338167092854233e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.528934543428048e-05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.858484533941923e-05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>9.737281239920756e-06</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5.264969369241459e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.510610496167743e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.936333727655033e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.38341770663391e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.522160756421042e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0001036960138583293</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4.926750096523728e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>7.248974146828752e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.86739355722974e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.774741938664776e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.719204092668209e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.508951155097091e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4.447069603132442e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.009640021976242e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.007732181885796e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7.116784585468712e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.090526927212572e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.702238401637669e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.041179399573034e-05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.038869169955991e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.732282792585878e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.889277340317607e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.337732703433525e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.066671643512234e-05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.064109944018358e-05</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.663462929443563e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.050353007123767e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.257753972229574e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.069875156734194e-05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.067285804113315e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7.971892214950133e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4.159642034321218e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4.726078141338847e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.072441508018339e-05</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.069829801474807e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.755713510819154e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.020960741839867e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5.806564481400829e-05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.07275665073883e-05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.070147981128566e-05</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0001611444339698201</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6.729488161494481e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>7.686224446848584e-05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.073020743806409e-05</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.070402762560438e-05</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0001833863402852508</v>
+      </c>
+      <c r="L13" t="n">
+        <v>7.174478469867268e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>8.123484902569726e-05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.073051651068948e-05</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.070434426409602e-05</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0002050723250325993</v>
+      </c>
+      <c r="L14" t="n">
+        <v>7.609400906287563e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>8.532040257396364e-05</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.073077412429925e-05</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.070459892672316e-05</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_3.xlsx
+++ b/Results/rbf_fd_parameter_study_3.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvector Angle" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3892,4 +3893,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.718919465984278e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3.89978867107578e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>6.766143666184266e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0001557021297320417</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4.294148207686093e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.002445410302574624</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0005110810380969428</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.001104660783757523</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0001278970938473387</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.827125693429671e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.002764172726189246</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0002857246442778727</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0004242833458168992</v>
+      </c>
+      <c r="N4" t="n">
+        <v>8.722912161039657e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.518936346848323e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0006097297281127284</v>
+      </c>
+      <c r="L5" t="n">
+        <v>9.849135969110968e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0001384075681304781</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.420113605840141e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.277480135608276e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.663462929443563e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.050353007123767e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.257753972229574e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.069875156734194e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.067285804113315e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0005303362416532484</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8.293128441297116e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.000112634881914266</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5.420727693286011e-05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.275372280646265e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0006512378501984249</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0001071510595492769</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0001499581608463119</v>
+      </c>
+      <c r="N8" t="n">
+        <v>8.724059109345258e-05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.518065301531853e-05</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8.550205792172972e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.736833409023401e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>6.791307567779247e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0001279190963253757</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.830257656406344e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.719147887009961e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3.899843607285988e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6.766460066750847e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0001557021396594715</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.294148235470184e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_3.xlsx
+++ b/Results/rbf_fd_parameter_study_3.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9D7B31-C612-4EEF-9B90-91D6417424AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,20 @@
     <sheet name="Eigenvalue Ratio" sheetId="4" r:id="rId5"/>
     <sheet name="Eigenvector Angle" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 

--- a/Results/rbf_fd_parameter_study_3.xlsx
+++ b/Results/rbf_fd_parameter_study_3.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,4 +1057,930 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.9860347500270991</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.4259664738268631</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.2499791977369225</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.07802738616956131</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.01915519610405978</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.9720549607907882</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.4202702642632494</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.2464332023827402</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0779974212506266</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.01914990030661555</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.01802726883604716</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.009389596909957365</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.008632905489548794</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.006093345854205279</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.005959538425397891</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.01417245300853199</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.007466452718449102</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.007055509679748803</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.005433987511848881</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.005314542747970282</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0001551158604397572</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6.874370387021538e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7.027382257959546e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7.334246771865775e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.69630941771951e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>9.549546173037029e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4.510752920497934e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4.592426653550046e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.834454741350037e-05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.177836899176362e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.646073260768891e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3.485235783419013e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.513697427610774e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5.179175786430957e-05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.594475813076061e-05</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001521841071904001</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7.62508771624119e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9.481328850186309e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>9.093965532829618e-05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.262584596634339e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.928355705866786e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.33606386726618e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.960227599648273e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7.348311465871189e-05</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.68841992026496e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.085046241613998e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.768518841617085e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.842976488132461e-05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.813795194099619e-05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.864781450911887e-05</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.659013755912045e-05</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.662145345023614e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0001385374292187936</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.001109602082638088</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0002210163818622357</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0003367523418771574</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.0001051972808217769</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.003274111667210744</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.006031589613116459</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.001187963556976787</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0003609795687131852</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0004800153061874261</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0009725181964368545</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.03288988632202786</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.006566787421767246</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.001474287482432885</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.001489090390660353</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.003028597112335894</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1053201933892508</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.02099673443181571</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="n">
+        <v>30</v>
+      </c>
+      <c r="E16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.0181819589335537</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.01258240122504106</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.0165703101649411</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.4956466107883791</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.09918420247912141</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_3.xlsx
+++ b/Results/rbf_fd_parameter_study_3.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1983,4 +1984,875 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.193711548182573</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.1265546300893096</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1525158247418608</v>
+      </c>
+      <c r="N2" t="n">
+        <v>7.282213727247959e-05</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.430901093114959e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9.473806784036631e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.746888127253181e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>7.840931439775386e-05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6.824387350499544e-05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.363465568628292e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5.08190427385561e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.831466633831803e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.479793416420557e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.577372023964463e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.266990984568442e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.560859044363377e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.759168328003473e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4.340446208952487e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.287045162686989e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.252412492857594e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0005394377244852728</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0001905529852158534</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0002348729000731807</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.733000943469892e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.609853822567167e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0003986311938371506</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0001353501757434012</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0001354852679676758</v>
+      </c>
+      <c r="N7" t="n">
+        <v>6.231071180579983e-05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4.891916897881257e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.001547248336003701</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0006646143944239299</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0008353845650536038</v>
+      </c>
+      <c r="N8" t="n">
+        <v>6.940218583815805e-05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>6.77993702878041e-05</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0002420117921556518</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001039556152744024</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0002176039760186583</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.376685904874472e-05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5.325210727501017e-06</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>115</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0001065742030289607</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4.698754953250704e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5.824767957785919e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.254175731238138e-05</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.210287072167179e-06</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>130</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0001790257195558931</v>
+      </c>
+      <c r="L11" t="n">
+        <v>8.197455387887459e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>7.377422358201529e-05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.119943291857881e-05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4.133157310992081e-06</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0006408515783324131</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.000199815097663867</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0001234718558283949</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.521389689646412e-05</v>
+      </c>
+      <c r="O12" t="n">
+        <v>5.263373315544121e-06</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>175</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0001137323665214766</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4.786449887741723e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.172519825621633e-05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.239237918356727e-05</v>
+      </c>
+      <c r="O13" t="n">
+        <v>6.771800954576566e-06</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0001324278456360001</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4.491720866005463e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.82671106824041e-05</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.730127458612524e-05</v>
+      </c>
+      <c r="O14" t="n">
+        <v>9.047214231691841e-06</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>250</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.495549592816649e-05</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.168464022487565e-05</v>
+      </c>
+      <c r="M15" t="n">
+        <v>6.783368180516107e-06</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6.588644532970156e-06</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.45525083365477e-06</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_3.xlsx
+++ b/Results/rbf_fd_parameter_study_3.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2855,4 +2856,655 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.081211629407415e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>8.229980940590832e-06</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.031678232264162e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.044851525052125e-05</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.100708172871776e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.121335330779065e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>8.359520282200614e-06</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.091794492597357e-05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.079198284025473e-05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.105700067114043e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.197373644304228e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8.613592011017406e-06</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.210659994663373e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.101587507849472e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.108728093758486e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.186348251697664e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8.57637986539482e-06</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.19113001640489e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.111170781974916e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.110389199539944e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.272885191899523e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8.833006438783031e-06</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.30287947828141e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.115400197686363e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.11107258313345e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.891865132485768e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.025470868611052e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.354956489936808e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>6.749866087607341e-05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.668135676120787e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.084626342380062e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.009281547812471e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.254882392508813e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>6.762277791915868e-05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.669980732279225e-05</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.928355705866786e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.33606386726618e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.960227599648273e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7.348311465871189e-05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.68841992026496e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0003925498135580269</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.9498380150766e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0002841774936687796</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7.490750296664226e-05</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.713155494657811e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0001131034689450556</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.253504951750308e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.265490434991435e-05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0001048432669074043</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.764309517694026e-05</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_3.xlsx
+++ b/Results/rbf_fd_parameter_study_3.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3507,4 +3508,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.137969786904177e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.021933283082026e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.479637771238399e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0001400510308801884</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.234035851797465e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.101807834610556e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>9.459671553879516e-06</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.418499337994968e-05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>9.337513009502973e-05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.800885356908714e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9.695826842688147e-06</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8.493438714552381e-06</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.190635634650204e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>6.103430219894944e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.584682057479854e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.718238037648196e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.0452799434933e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4.407479198756492e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6.696408514070662e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.621615584418795e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0001344164100128556</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5.769529142713946e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.00032145672025569</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7.217700322843047e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.672970095625332e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.958894990967598e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.551921893239716e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6.334980087608754e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>7.286101482347252e-05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.680937109663819e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.882784787214055e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.058200847791811e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.485984405921567e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7.341368787362111e-05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.687573778157849e-05</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.928355705866786e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.33606386726618e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.960227599648273e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7.348311465871189e-05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.68841992026496e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0002779857087453418</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.856750747938597e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0002484117211090988</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7.35387149256267e-05</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.689099585579853e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0001789745325137124</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.177970910104677e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0001507901878821182</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7.35456698178331e-05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.689184738830352e-05</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0001463237754262209</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4.585177377027717e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0001072992454215751</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7.355123145669023e-05</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.689252846530946e-05</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0001436118798415313</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4.459425992642147e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0001034694444055838</v>
+      </c>
+      <c r="N13" t="n">
+        <v>7.35519259832579e-05</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.689261362072184e-05</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0001416348173695795</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4.369534047025134e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0001006039444778614</v>
+      </c>
+      <c r="N14" t="n">
+        <v>7.355248381910692e-05</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.689268176686159e-05</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_3.xlsx
+++ b/Results/rbf_fd_parameter_study_3.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Eigenvector Angle" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4324,4 +4325,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.506048269970743e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.512599505377078e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>9.485203636677051e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0002588758964779837</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.738095173786427e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.454811353918007e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.720514473993147e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>8.55586473872033e-05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>7.830538618388664e-05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.307904740083761e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.754455360906301e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.163456337753736e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.98673552689388e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5.99066095298833e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.401182294951453e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.847462848741463e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.513832091452029e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4.248091241636988e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6.832267493753605e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.554202953500943e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.928355705866786e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.33606386726618e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.960227599648273e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7.348311465871189e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.68841992026496e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.188015941711012e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.153508604905075e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.671207933656977e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>6.968935962901231e-05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.558696929243952e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.503699518074831e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.109271007459259e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.454629729544206e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>6.210934286528343e-05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.406826280938521e-05</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.466139959944971e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.49578324209761e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.479763219704341e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5.83270869804066e-05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.311565452768625e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.506056679329141e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.512601965333277e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>9.485239672328497e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0002588758932102305</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.73809521750964e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_3.xlsx
+++ b/Results/rbf_fd_parameter_study_3.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1166,4 +1167,930 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>17741.80603158191</v>
+      </c>
+      <c r="L2" t="n">
+        <v>17747.96208077488</v>
+      </c>
+      <c r="M2" t="n">
+        <v>17749.92483180566</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.9999662115306949</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.9999436586851478</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4434.701444224702</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4436.240492602554</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4436.731090007683</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.9997971672111443</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.9997746347394439</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9.519194880142126e-06</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9.517923252419754e-06</v>
+      </c>
+      <c r="M4" t="n">
+        <v>9.518964540545242e-06</v>
+      </c>
+      <c r="N4" t="n">
+        <v>9.519765098907662e-06</v>
+      </c>
+      <c r="O4" t="n">
+        <v>9.518873731667283e-06</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.65448399958965e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.54969293337932e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.548937131749156e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.587454808323011e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.54877754924816e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.455686068075696e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.456187174251193e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.4563468286715e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.457947876526166e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.456325628946679e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.385764059767922e-06</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6.385399337769255e-06</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6.386098509862005e-06</v>
+      </c>
+      <c r="N7" t="n">
+        <v>6.387684260054211e-06</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6.386057700047674e-06</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.732298739003437e-06</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.722180156813765e-06</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.722457905100538e-06</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.723998107846865e-06</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.722462961609679e-06</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.257550920031117e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.255923167980521e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.256059147244413e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.256393271299744e-05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.256074741977432e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.279254958670487e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.276273665739278e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.27651993665991e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.277079607182427e-05</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.276571416239317e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>500</v>
+      </c>
+      <c r="B11" t="n">
+        <v>500</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.213226233995509e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.20473481956956e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.205182946227613e-05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.20666703425068e-05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4.205358415209945e-05</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>500</v>
+      </c>
+      <c r="B12" t="n">
+        <v>500</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.309190313805587e-05</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5.25691205881037e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5.257173274803643e-05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.264093143353984e-05</v>
+      </c>
+      <c r="O12" t="n">
+        <v>5.257414651948826e-05</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>500</v>
+      </c>
+      <c r="B13" t="n">
+        <v>500</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8.099253594340561e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>8.000766593832508e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>7.99943702855884e-05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8.015120445576896e-05</v>
+      </c>
+      <c r="O13" t="n">
+        <v>7.998551260189589e-05</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>500</v>
+      </c>
+      <c r="B14" t="n">
+        <v>500</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.001412056886883444</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.001407207236179255</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.00140732682143689</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.001406208003271254</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.001405345614895977</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>500</v>
+      </c>
+      <c r="B15" t="n">
+        <v>500</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.005662997704063531</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.005647316334646892</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.005647839243587692</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.005618864952597752</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.005616114696752194</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>500</v>
+      </c>
+      <c r="B16" t="n">
+        <v>500</v>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.03399219029280272</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.0338839648674342</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.03388688320774091</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.03279026849362687</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.03277625144703095</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_3.xlsx
+++ b/Results/rbf_fd_parameter_study_3.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2093,4 +2094,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.279254958670487e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.276273665739278e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.27651993665991e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.277079607182427e-05</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.276571416239317e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.282137308656475e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.275462270728093e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.275701678669325e-05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.27742671454389e-05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.275754350759826e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.165721278751815e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4.157487341016203e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4.159838703754531e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.15889198283367e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4.158105110019858e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0005857282255990101</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0004205678811918317</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0002611473466210117</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0001052282181499117</v>
+      </c>
+      <c r="O5" t="n">
+        <v>9.643341072055402e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.005917715119587206</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.00227282378076361</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.002266324650882305</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0001218096152803307</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0001188486967134109</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0002392526524520825</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0001644129816478592</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0003207008808450671</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0001572820744715193</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0001572827036863561</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1341276268354471</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.04703961462521345</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.05805294087714888</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0002661942475306844</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.000249583087833814</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0005634714290097753</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0003851619136891987</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0003908892188953638</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0003451389083187449</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0003382484128016606</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>65</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.004491438757616907</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.001576130086014728</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.001940871385230707</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0004353189476202258</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0004142107204575014</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_3.xlsx
+++ b/Results/rbf_fd_parameter_study_3.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2690,4 +2691,655 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.279254958670487e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.276273665739278e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.27651993665991e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.277079607182427e-05</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.276571416239317e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.280614224069377e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.277635920071262e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.277882347883164e-05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.278479193371362e-05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.277933890873181e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.279977263056682e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.276619993540352e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.276865837352035e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.277789816195622e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.276917292813149e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.279309069498739e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.27633554889152e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.276581851508077e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.27712979720953e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.276633336748232e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.278591271211846e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.27562699871962e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.275873227921031e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.276433980924696e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.275924681222946e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.278527846580634e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.275545610741911e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.275791804801892e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.276344510218899e-05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.27584325194026e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.278747520359136e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.275778890527514e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.27602512289028e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.276579149539184e-05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.276076585707055e-05</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.279122588415386e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.276156893543931e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.276403178931762e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.276972388799934e-05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.276454657812169e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.278491210282157e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.275547586194261e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.275793903024418e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.276787085878809e-05</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.275845371422194e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>500</v>
+      </c>
+      <c r="B11" t="n">
+        <v>500</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.278105566777869e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.275141296841286e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.27538764771491e-05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.277189042238915e-05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.275439131981445e-05</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_3.xlsx
+++ b/Results/rbf_fd_parameter_study_3.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3342,4 +3343,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.17943255262265e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.177698581810639e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.177761874775688e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.179435585838643e-05</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.177747264507537e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.938054635770015e-07</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6.730780053160151e-07</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6.727003218195146e-07</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6.840740329000297e-07</v>
+      </c>
+      <c r="O3" t="n">
+        <v>6.725319944049211e-07</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.623527475560984e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.620629442734884e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.620787275989071e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.621640053965564e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.620812961286924e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.934482001863629e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.931544062951689e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.931742316085042e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.93245988132487e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.93177918478526e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.207879672354649e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.204874170310383e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.205110255642824e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.205702672083352e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.205158519549358e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.24373948117319e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.240739199039189e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.240980395597808e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.241555809517805e-05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.241030265478299e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.272703502344463e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.269717910304867e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.269963250001722e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.270525335552625e-05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.270014433744097e-05</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.276341449912488e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.273358388641259e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.273604247169842e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.274164883560182e-05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.273655596004646e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.279254958670487e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.276273665739278e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.27651993665991e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.277079607182427e-05</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.276571416239317e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>500</v>
+      </c>
+      <c r="B11" t="n">
+        <v>500</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.279619900486348e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.276638233669338e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.276884555298586e-05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.277443886513257e-05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.276936047913894e-05</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>500</v>
+      </c>
+      <c r="B12" t="n">
+        <v>500</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.279915489300507e-05</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.276929957227753e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.277176318374656e-05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.277735298850972e-05</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.277227823513418e-05</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>500</v>
+      </c>
+      <c r="B13" t="n">
+        <v>500</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.279954405489729e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.276966367408947e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.277212733202059e-05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.277771769147244e-05</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.27726424205735e-05</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>500</v>
+      </c>
+      <c r="B14" t="n">
+        <v>500</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.279989796075057e-05</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.276995516393766e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.277241885705809e-05</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.277801073200963e-05</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.277293399345708e-05</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_3.xlsx
+++ b/Results/rbf_fd_parameter_study_3.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Eigenvector Angle" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4159,4 +4160,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.229071144096043e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4.228568992991788e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4.228598926633127e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.232147529692086e-05</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4.228420260232138e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.4284687405769049</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.3707475505722052</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.512888771216489</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8632573765213453</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.6518963944500923</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.4372380016124498</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.3824097390334052</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.4220872714078632</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5988735061828119</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.5122211308090457</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.3581138384950461</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.318493683023698</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.297172949411881</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.3706664421646093</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.3462996446614576</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.279254958670487e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.276273665739278e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.27651993665991e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.277079607182427e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.276571416239317e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.3581168084118269</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3184936829919129</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2971729443352181</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.3706664370679708</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.3462996449598224</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.4372396672879994</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.3824097390354</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.4220872667967276</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5988734787992519</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5122211316392088</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.4284689883853721</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.370747550612324</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.5128887694450289</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.8632573587110896</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.6518963964210512</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.229071144096043e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4.228568992993103e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4.228598926634406e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.232147529692086e-05</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.228420260232138e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>